--- a/output/pdf_financials_xlsx/KLT.H.xlsx
+++ b/output/pdf_financials_xlsx/KLT.H.xlsx
@@ -1264,10 +1264,10 @@
         <v>-4.406746</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.266655</v>
+        <v>-4.266655</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.967604</v>
+        <v>-2.967604</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-2.303105</v>
@@ -1552,10 +1552,10 @@
         <v>-4.406746</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.266655</v>
+        <v>-4.266655</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.967604</v>
+        <v>-2.967604</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-2.303105</v>
@@ -1723,10 +1723,10 @@
         <v>-4.406746</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.266655</v>
+        <v>-4.266655</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.967604</v>
+        <v>-2.967604</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-2.303105</v>
@@ -1894,10 +1894,10 @@
         <v>44.06746</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-53.333188</v>
+        <v>53.333188</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-74.1901</v>
+        <v>74.1901</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
         <v>-4.406746</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.266655</v>
+        <v>-4.266655</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.967604</v>
+        <v>-2.967604</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-2.303105</v>
@@ -2069,10 +2069,10 @@
         <v>-4.406746</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.266655</v>
+        <v>-4.266655</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.967604</v>
+        <v>-2.967604</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-2.303105</v>
@@ -2213,10 +2213,10 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -5621,19 +5621,19 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.007334</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.031369</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.114225</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.091808</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.088061</v>
       </c>
       <c r="L91" s="3" t="n">
         <v>0</v>
@@ -10842,7 +10842,11 @@
           <t>Cumulative translation reserve</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11944,7 +11948,11 @@
           <t>Cumulative Translation Reserve</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -33615,10 +33623,10 @@
         <v>-4.406746</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>4.266655</v>
+        <v>-4.266655</v>
       </c>
       <c r="M271" s="5" t="n">
-        <v>2.967604</v>
+        <v>-2.967604</v>
       </c>
       <c r="N271" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KLT.H.xlsx
+++ b/output/pdf_financials_xlsx/KLT.H.xlsx
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.038309</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004595</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018207</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008947999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.047364</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01465</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008881</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002594</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000662</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1934,31 +1934,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.622842</v>
+        <v>-2.584533</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.022327</v>
+        <v>-2.017732</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.671751</v>
+        <v>-11.653544</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.92195</v>
+        <v>-3.913002</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.724875</v>
+        <v>-2.677511</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.103837</v>
+        <v>-4.089187</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.406746</v>
+        <v>-4.397865</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.266655</v>
+        <v>-4.264061</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.967604</v>
+        <v>-2.966942</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-2.303105</v>
@@ -2048,31 +2048,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.622842</v>
+        <v>-2.584533</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.022327</v>
+        <v>-2.017732</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.671751</v>
+        <v>-11.653544</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.92195</v>
+        <v>-3.913002</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.724875</v>
+        <v>-2.677511</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.103837</v>
+        <v>-4.089187</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.406746</v>
+        <v>-4.397865</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.266655</v>
+        <v>-4.264061</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.967604</v>
+        <v>-2.966942</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-2.303105</v>
@@ -29244,7 +29244,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -39140,7 +39140,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E329" s="5" t="n">

--- a/output/pdf_financials_xlsx/KLT.H.xlsx
+++ b/output/pdf_financials_xlsx/KLT.H.xlsx
@@ -733,13 +733,13 @@
         <v>1.055482</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.379643</v>
+        <v>1.418066</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.393269</v>
+        <v>1.424587</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.203814</v>
+        <v>2.271148</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -904,13 +904,13 @@
         <v>1.055482</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.379643</v>
+        <v>1.418066</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.393269</v>
+        <v>1.424587</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2.203814</v>
+        <v>2.271148</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -961,13 +961,13 @@
         <v>-1.055482</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.379643</v>
+        <v>-1.418066</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.393269</v>
+        <v>-1.424587</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-2.203814</v>
+        <v>-2.271148</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -6652,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.011839</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -18632,7 +18632,11 @@
           <t>Accretion expense (note 5)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -38296,7 +38300,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -43080,7 +43088,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
